--- a/public/downloads/sample_excels/mobile_models_import_sample.xlsx
+++ b/public/downloads/sample_excels/mobile_models_import_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub 2024\HSBR-Apps\Fixancare app\fixancare\public\downloads\sample_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A98BC8A-E5EF-40F2-A014-CFB94144FE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4B2530-E38F-44B8-9911-74ED3C9CA942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BEBF86B8-2F91-4EC2-8B46-CAF70645DC37}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="15600" windowHeight="11310" xr2:uid="{BEBF86B8-2F91-4EC2-8B46-CAF70645DC37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
     <t>status</t>
   </si>
   <si>
-    <t>brand_id</t>
-  </si>
-  <si>
     <t>mobile_model_code</t>
   </si>
   <si>
     <t>mobile_model_name</t>
+  </si>
+  <si>
+    <t>brand_name</t>
   </si>
 </sst>
 </file>
@@ -410,13 +410,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
